--- a/templates/题库模板.xlsx
+++ b/templates/题库模板.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">题型</t>
   </si>
@@ -165,6 +165,51 @@
   </si>
   <si>
     <t xml:space="preserve">行测·资料分析</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024年1—2月，该示范区规模以上高新技术企业实现总收入约为多少亿元？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4890.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4990.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5078.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5180.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表中已直接给出 2024 年 1—2 月总收入 4990.5 亿元；也可用基期量公式验证：5280.0 ÷ (1 + 5.8%) ≈ 4990.5。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">资料分析·基期量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025年1—2月，该示范区研究开发费用合计占规模以上高新技术企业总收入的比重约为？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比重 = 部分 ÷ 整体 = 611.9 ÷ 5280.0 ≈ 11.6%。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">资料分析·比重</t>
   </si>
 </sst>
 </file>
@@ -368,6 +413,106 @@
         <v>26</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/templates/题库模板.xlsx
+++ b/templates/题库模板.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="题库" sheetId="1" r:id="rId1"/>
+    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t xml:space="preserve">题型</t>
   </si>
@@ -17,6 +18,9 @@
   </si>
   <si>
     <t xml:space="preserve">材料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图片</t>
   </si>
   <si>
     <t xml:space="preserve">选项A</t>
@@ -210,6 +214,57 @@
   </si>
   <si>
     <t xml:space="preserve">资料分析·比重</t>
+  </si>
+  <si>
+    <t xml:space="preserve">题库模板 · 使用说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（本表只是说明，导入时会被自动跳过）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么导入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在「题库」表里填题（一行一题，表头别改），App 里点「导入」选这个文件。统一只支持 Excel（.xlsx）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">带图片怎么导</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图片多时做成题库包：把 题库.xlsx 和图片文件夹（如 images/）一起压成 zip 再导入（见 题库包模板.zip）；材料 / 图片列里写 images/xxx.png 这样的包内相对路径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必填列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只有「题干」必填，其余列全部可以留空</t>
+  </si>
+  <si>
+    <t xml:space="preserve">留空按单选；多选 / 判断 / 不定项要写清楚；多选答案用逗号分隔（如 A,C,D）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可以整列先空着 = 待补答案。导完先做题，之后在成绩报告页「补答案」：逐题填，或导入文件（答案模板.xlsx），会按你的作答自动重判</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可以整列先空着。之后导入「解析模板.xlsx」（题号 + 解析两列），App 自动识别、只补解析不动答案</t>
+  </si>
+  <si>
+    <t xml:space="preserve">填图片地址，多张用 | 分隔；支持手机本地路径、content://、base64；题库包里写包内相对路径（见 题库包模板.zip）。图片会显示在材料顶部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大段文字（含表格）放这里；支持 Markdown 表格、内嵌图片 ![](路径)、自绘图 :::chart。同一道题的材料和图片都写在它自己的行里</t>
+  </si>
+  <si>
+    <t xml:space="preserve">选项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最多到 H 列，用不到的留空即可</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更多帮助</t>
+  </si>
+  <si>
+    <t xml:space="preserve">格式细节见 docs/02-题库格式规范.md；答案 / 解析后补见 docs/04-答案后补.md；题库包见 docs/03-题库包.md</t>
   </si>
 </sst>
 </file>
@@ -266,18 +321,19 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2"/>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D2"/>
       <c r="E2" t="s">
         <v>20</v>
       </c>
@@ -312,20 +368,21 @@
         <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3"/>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
+      <c r="D3"/>
       <c r="E3" t="s">
         <v>34</v>
       </c>
@@ -348,7 +405,7 @@
         <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -360,22 +417,23 @@
         <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" t="s">
         <v>43</v>
       </c>
+      <c r="D4"/>
       <c r="E4" t="s">
         <v>44</v>
       </c>
@@ -395,37 +453,38 @@
         <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D5"/>
       <c r="E5" t="s">
         <v>53</v>
       </c>
@@ -436,46 +495,47 @@
         <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J5" t="s">
         <v>57</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
         <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D6"/>
       <c r="E6" t="s">
         <v>60</v>
       </c>
@@ -495,22 +555,120 @@
         <v>65</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N6" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="O6" t="s">
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
